--- a/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo</t>
+          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 16,09</t>
+          <t>10,57; 15,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,71</t>
+          <t>10,27; 12,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,98</t>
+          <t>8,39; 10,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 12,23</t>
+          <t>11,0; 12,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 12,36</t>
+          <t>10,68; 12,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,46</t>
+          <t>7,46; 10,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,54</t>
+          <t>11,37; 13,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 12,18</t>
+          <t>10,8; 12,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 10,37</t>
+          <t>8,21; 10,29</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 11,62</t>
+          <t>9,61; 11,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 11,69</t>
+          <t>10,11; 11,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,45</t>
+          <t>9,3; 11,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 11,79</t>
+          <t>9,5; 11,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 12,96</t>
+          <t>10,83; 12,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,17</t>
+          <t>8,5; 11,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 11,5</t>
+          <t>9,88; 11,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,83; 12,05</t>
+          <t>10,81; 12,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 10,98</t>
+          <t>9,14; 10,86</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 11,85</t>
+          <t>9,74; 11,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 12,0</t>
+          <t>10,29; 11,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,18</t>
+          <t>7,77; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 11,65</t>
+          <t>10,01; 11,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 11,78</t>
+          <t>9,81; 11,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 10,4</t>
+          <t>8,7; 10,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,49</t>
+          <t>10,26; 11,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 11,5</t>
+          <t>10,31; 11,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 9,94</t>
+          <t>8,57; 9,95</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 12,06</t>
+          <t>9,34; 12,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 14,34</t>
+          <t>10,47; 13,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 10,96</t>
+          <t>8,61; 10,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,84</t>
+          <t>10,41; 12,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 10,97</t>
+          <t>9,39; 10,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,31</t>
+          <t>7,62; 10,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,04</t>
+          <t>10,33; 12,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 12,43</t>
+          <t>10,33; 12,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,26</t>
+          <t>8,58; 10,32</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 11,95</t>
+          <t>10,46; 11,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 11,99</t>
+          <t>10,76; 12,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,46</t>
+          <t>9,14; 10,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 11,81</t>
+          <t>10,7; 11,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,63</t>
+          <t>10,68; 11,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,99</t>
+          <t>8,7; 9,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 11,68</t>
+          <t>10,78; 11,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 11,62</t>
+          <t>10,9; 11,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,94</t>
+          <t>9,05; 9,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 15,94</t>
+          <t>10,81; 16,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 12,71</t>
+          <t>10,34; 12,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 10,89</t>
+          <t>8,33; 10,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,2</t>
+          <t>11,06; 12,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,41</t>
+          <t>10,65; 12,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,46</t>
+          <t>7,38; 10,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 13,65</t>
+          <t>11,27; 13,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,2</t>
+          <t>10,75; 12,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,29</t>
+          <t>8,21; 10,3</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 11,51</t>
+          <t>9,67; 11,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 11,79</t>
+          <t>10,17; 11,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 11,6</t>
+          <t>9,31; 11,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 11,77</t>
+          <t>9,58; 11,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,83; 12,76</t>
+          <t>10,91; 12,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,37</t>
+          <t>8,48; 11,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 11,49</t>
+          <t>9,94; 11,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 12,02</t>
+          <t>10,81; 12,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,86</t>
+          <t>9,19; 10,99</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,74; 11,82</t>
+          <t>9,66; 11,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 11,93</t>
+          <t>10,32; 11,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 10,1</t>
+          <t>7,74; 10,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 11,66</t>
+          <t>10,04; 11,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 11,67</t>
+          <t>9,78; 11,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 10,31</t>
+          <t>8,64; 10,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,53</t>
+          <t>10,24; 11,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 11,5</t>
+          <t>10,31; 11,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 9,95</t>
+          <t>8,55; 10,04</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 12,04</t>
+          <t>9,39; 12,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 13,7</t>
+          <t>10,5; 14,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 10,76</t>
+          <t>8,63; 10,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,81</t>
+          <t>10,43; 12,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 10,99</t>
+          <t>9,45; 10,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,45</t>
+          <t>7,62; 10,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,11</t>
+          <t>10,3; 12,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,38</t>
+          <t>10,35; 12,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,32</t>
+          <t>8,58; 10,3</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,95</t>
+          <t>10,38; 11,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,13</t>
+          <t>10,8; 12,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,35</t>
+          <t>9,12; 10,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,81</t>
+          <t>10,67; 11,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,68</t>
+          <t>10,69; 11,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 9,99</t>
+          <t>8,73; 10,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,73</t>
+          <t>10,77; 11,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 11,72</t>
+          <t>10,86; 11,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,99</t>
+          <t>9,11; 9,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13,35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,62</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,19</t>
+          <t>10,99; 12,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,79</t>
+          <t>10,64; 12,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,91</t>
+          <t>7,52; 10,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 12,24</t>
+          <t>10,48; 16,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 12,41</t>
+          <t>10,2; 12,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,36</t>
+          <t>8,4; 10,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 13,6</t>
+          <t>11,38; 13,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 12,25</t>
+          <t>10,72; 12,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,3</t>
+          <t>8,05; 10,37</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,79</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,68</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,95</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,26</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,82</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,79</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 11,57</t>
+          <t>9,51; 11,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 11,75</t>
+          <t>10,98; 12,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,41</t>
+          <t>8,49; 11,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 11,84</t>
+          <t>9,71; 11,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,91; 12,88</t>
+          <t>10,2; 11,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,28</t>
+          <t>9,22; 11,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 11,46</t>
+          <t>9,86; 11,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 12,09</t>
+          <t>10,83; 12,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 10,99</t>
+          <t>9,16; 10,98</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,71</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,53</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>11,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,71</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,79</t>
+          <t>10,12; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 11,97</t>
+          <t>9,83; 11,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,13</t>
+          <t>8,69; 10,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 11,64</t>
+          <t>9,76; 11,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 11,67</t>
+          <t>10,31; 12,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 10,38</t>
+          <t>7,73; 10,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 11,51</t>
+          <t>10,26; 11,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 11,61</t>
+          <t>10,28; 11,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 10,04</t>
+          <t>8,48; 9,94</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,03</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>11,66</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,52</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,03</t>
+          <t>10,48; 12,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 14,03</t>
+          <t>9,49; 10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,95</t>
+          <t>7,56; 10,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,75</t>
+          <t>9,23; 12,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,96</t>
+          <t>10,57; 14,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,39</t>
+          <t>8,68; 10,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 12,1</t>
+          <t>10,35; 12,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,38</t>
+          <t>10,29; 12,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,3</t>
+          <t>8,58; 10,26</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,35</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>11,21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,3</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,96</t>
+          <t>10,65; 11,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,08</t>
+          <t>10,68; 11,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,29</t>
+          <t>8,71; 9,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,81</t>
+          <t>10,37; 11,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,62</t>
+          <t>10,8; 11,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,02</t>
+          <t>9,18; 10,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,77; 11,69</t>
+          <t>10,81; 11,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,86; 11,66</t>
+          <t>10,87; 11,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,98</t>
+          <t>9,06; 9,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,64</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,62</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,83</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,25</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,53</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9,33</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>11.63654529094775</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>11.46055823830758</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.064511851372597</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>13.34607465416724</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>11.61838311925949</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>9.832689688652071</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>12.25378579051623</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>11.5274421935102</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>9.331842342055241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10,99; 12,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10,64; 12,36</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 10,46</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10,48; 16,09</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,2; 12,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,4; 10,98</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,38; 13,54</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10,72; 12,18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8,05; 10,37</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>10.98796513244004</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>10.64182599604151</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>7.524287157179935</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10.48324764322325</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>10.19770397924865</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>8.404617502631732</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11.37979799684378</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>10.71583127631248</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8.048363039685317</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.23143873234466</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.35959145152669</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.46407499569912</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16.09062102593236</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>12.70989443564624</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.97633476987686</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>13.54478150377208</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>12.17977577000793</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>10.36789960769039</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,82</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,79</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,68</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,95</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,26</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,76</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,39</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 11,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,98; 12,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,49; 11,17</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 11,62</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,2; 11,69</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,22; 11,45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,86; 11,5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10,83; 12,05</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,16; 10,98</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>10.82315475794445</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>11.79499807121098</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.67792269440511</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10.67772042491308</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>10.94687070458338</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>10.25743756000493</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>10.76437590564549</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11.39424406005595</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9.974784646255717</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>11,07</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,71</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,83</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,02</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,89</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,96</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10,9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9.512079341473793</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>10.98366185904644</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>8.487128264929504</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9.708162349253529</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>10.20323718688267</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>9.223349123045192</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>9.857915008053309</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>10.82698092088194</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>9.163741240041315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,12; 11,65</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,83; 11,78</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,69; 10,4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,76; 11,85</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>10,31; 12,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,73; 10,18</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,26; 11,49</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10,28; 11,5</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>8,48; 9,94</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.79110138564247</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>12.95591646597281</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.17278723519991</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11.62402415151224</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11.68798193918911</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>11.4508008969521</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>11.49566010311536</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>12.0450422634986</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>10.97680587984323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>11,6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10,3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,66</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,52</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11,02</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9,33</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>11.06819619149895</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10.70822673396891</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.530356333277963</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10.83044294024416</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>11.01565075990586</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>8.885927033800135</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>10.96086392627521</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>10.89624653143087</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.252117156162138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,48; 12,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9,49; 10,97</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7,56; 10,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,23; 12,06</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,57; 14,34</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,68; 10,96</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,35; 12,04</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10,29; 12,43</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8,58; 10,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>10.12483611132774</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.831704035941737</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8.694767890501417</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>9.761061463513116</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10.30550673175724</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>7.728908213210244</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10.25694630658318</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>10.27671127011368</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>8.477606399976821</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.6507493258368</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.77977085058273</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.398722742663</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.85440232954325</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>11.99559173809453</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10.18262302909775</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>11.49127804194505</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>11.50237181516205</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.943786594358311</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>11.60146291749435</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>10.29647336857891</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9.030811396290755</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>10.99548950788695</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>11.65905822764129</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>9.518028223641203</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>11.29535794801509</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>11.01556918600673</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9.33420166124362</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>10.48052182257103</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>9.489812935802917</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.561549726735229</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>9.226336886175304</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>10.57488613554114</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>8.683297980067515</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>10.34971080762907</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>10.28998132523591</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8.576390745630652</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>12.83955700843843</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.96953608285979</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.31153499177826</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>12.06447474055066</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>14.34479790538158</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>10.9601130936855</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>12.04348227805146</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>12.43048698384045</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>10.2552879608454</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11,22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 11,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10,68; 11,63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 9,99</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10,37; 11,95</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 11,99</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 10,46</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,81; 11,68</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 11,62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 9,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>11.28417301559822</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>11.14422777139552</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>9.34668281645331</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>11.20630757442294</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>11.30324518534518</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>9.7089233786826</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>11.24963825833229</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>11.22417108368449</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>9.525522734041665</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>10.64809667044202</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>10.67999182304633</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>8.71068908156084</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>10.37498581962022</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>10.80123575423183</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>9.18391918169867</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>10.80931831765325</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>10.87275952914075</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>9.062670232824527</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11.80988921387442</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.62985829075116</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.985202220271852</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.94753713746618</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>11.99059437484276</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>10.45868568067961</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>11.67686966790702</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>11.62135942144971</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>9.939004192378006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
